--- a/outputs/daily/hr_rankings_2026-10-18_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-18_full.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>51.6</v>
+        <v>53.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>21.5</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S2" t="n">
         <v>92.09999999999999</v>
@@ -996,8 +996,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1036,7 +1044,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1060,7 +1068,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>47.5</v>
+        <v>50.1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,7 +1082,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1092,10 @@
         <v>28.5</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1097,39 +1105,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1272,8 +1276,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1312,7 +1324,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1336,7 +1348,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>45.5</v>
+        <v>48.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1362,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1372,10 @@
         <v>28.5</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -1373,39 +1385,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1548,8 +1556,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1588,7 +1604,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1612,7 +1628,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>44.7</v>
+        <v>46.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1636,7 +1652,7 @@
         <v>21.5</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S5" t="n">
         <v>95.5</v>
@@ -1824,8 +1840,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1864,7 +1888,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1888,7 +1912,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>43.3</v>
+        <v>45.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1912,7 +1936,7 @@
         <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S6" t="n">
         <v>88.7</v>
@@ -2100,8 +2124,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2140,7 +2172,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2164,7 +2196,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.3</v>
+        <v>45.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2188,7 +2220,7 @@
         <v>21.5</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S7" t="n">
         <v>90.40000000000001</v>
@@ -2376,8 +2408,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2416,7 +2456,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2440,7 +2480,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>42.1</v>
+        <v>44.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,7 +2494,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2464,10 +2504,10 @@
         <v>28.5</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -2477,39 +2517,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2652,8 +2688,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2672,7 +2716,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2692,7 +2736,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2716,7 +2760,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>40.4</v>
+        <v>43</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,7 +2774,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2740,10 +2784,10 @@
         <v>26.9</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -2753,39 +2797,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2928,8 +2968,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2968,7 +3016,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2992,7 +3040,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>38.8</v>
+        <v>41.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,7 +3054,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3016,10 +3064,10 @@
         <v>26.9</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -3029,39 +3077,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3204,8 +3248,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3244,7 +3296,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3320,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>35.7</v>
+        <v>38.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,7 +3334,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3292,10 +3344,10 @@
         <v>28.5</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -3305,39 +3357,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -3480,8 +3528,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3520,7 +3576,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3544,7 +3600,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>34.8</v>
+        <v>36.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3568,7 +3624,7 @@
         <v>21.5</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S12" t="n">
         <v>81.90000000000001</v>
@@ -3756,8 +3812,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3796,7 +3860,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3820,7 +3884,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>33.7</v>
+        <v>36.4</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,7 +3898,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3844,10 +3908,10 @@
         <v>28.5</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S13" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -3857,39 +3921,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4032,8 +4092,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4072,7 +4140,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4096,7 +4164,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>31.1</v>
+        <v>33.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,7 +4178,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4120,10 +4188,10 @@
         <v>26.9</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -4133,39 +4201,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4308,8 +4372,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4348,7 +4420,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4372,7 +4444,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.7</v>
+        <v>32.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4396,7 +4468,7 @@
         <v>21.5</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S15" t="n">
         <v>47.9</v>
@@ -4584,8 +4656,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4624,7 +4704,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4648,7 +4728,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>29.8</v>
+        <v>31.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4672,7 +4752,7 @@
         <v>21.5</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S16" t="n">
         <v>59.8</v>
@@ -4860,8 +4940,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4900,7 +4988,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4924,7 +5012,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.1</v>
+        <v>31.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,7 +5026,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -4948,10 +5036,10 @@
         <v>28.5</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
@@ -4961,39 +5049,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5136,8 +5220,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -5176,7 +5268,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5200,7 +5292,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>24.7</v>
+        <v>26.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5224,7 +5316,7 @@
         <v>21.5</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S18" t="n">
         <v>71.7</v>
@@ -5412,8 +5504,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -5452,7 +5552,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5476,7 +5576,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>24.6</v>
+        <v>26.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5500,7 +5600,7 @@
         <v>20.1</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S19" t="n">
         <v>40.2</v>
@@ -5688,8 +5788,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6054,7 +6162,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6078,7 +6186,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>51.6</v>
+        <v>53.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6102,7 +6210,7 @@
         <v>21.5</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S2" t="n">
         <v>92.09999999999999</v>
@@ -6290,8 +6398,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6330,7 +6446,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6354,7 +6470,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>47.5</v>
+        <v>50.1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,7 +6484,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6494,10 @@
         <v>28.5</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -6391,39 +6507,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6566,8 +6678,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6606,7 +6726,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6630,7 +6750,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>45.5</v>
+        <v>48.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6764,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6774,10 @@
         <v>28.5</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -6667,39 +6787,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -6842,8 +6958,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6882,7 +7006,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6906,7 +7030,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>44.7</v>
+        <v>46.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6930,7 +7054,7 @@
         <v>21.5</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S5" t="n">
         <v>95.5</v>
@@ -7118,8 +7242,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7158,7 +7290,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7182,7 +7314,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>43.3</v>
+        <v>45.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7206,7 +7338,7 @@
         <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S6" t="n">
         <v>88.7</v>
@@ -7394,8 +7526,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7434,7 +7574,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7458,7 +7598,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.3</v>
+        <v>45.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7482,7 +7622,7 @@
         <v>21.5</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S7" t="n">
         <v>90.40000000000001</v>
@@ -7670,8 +7810,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7710,7 +7858,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7734,7 +7882,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>42.1</v>
+        <v>44.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,7 +7896,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -7758,10 +7906,10 @@
         <v>28.5</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -7771,39 +7919,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7946,8 +8090,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7966,7 +8118,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7986,7 +8138,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8010,7 +8162,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>40.4</v>
+        <v>43</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,7 +8176,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8034,10 +8186,10 @@
         <v>26.9</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -8047,39 +8199,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8222,8 +8370,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8262,7 +8418,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8286,7 +8442,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>38.8</v>
+        <v>41.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,7 +8456,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8310,10 +8466,10 @@
         <v>26.9</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -8323,39 +8479,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8498,8 +8650,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8538,7 +8698,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8722,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>35.7</v>
+        <v>38.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,7 +8736,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -8586,10 +8746,10 @@
         <v>28.5</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -8599,39 +8759,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -8774,8 +8930,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8814,7 +8978,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8838,7 +9002,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>34.8</v>
+        <v>36.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8862,7 +9026,7 @@
         <v>21.5</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S12" t="n">
         <v>81.90000000000001</v>
@@ -9050,8 +9214,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9090,7 +9262,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9114,7 +9286,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>33.7</v>
+        <v>36.4</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,7 +9300,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -9138,10 +9310,10 @@
         <v>28.5</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S13" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -9151,39 +9323,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9326,8 +9494,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9366,7 +9542,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9390,7 +9566,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>31.1</v>
+        <v>33.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,7 +9580,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9414,10 +9590,10 @@
         <v>26.9</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -9427,39 +9603,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9602,8 +9774,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9642,7 +9822,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9666,7 +9846,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.7</v>
+        <v>32.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9690,7 +9870,7 @@
         <v>21.5</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S15" t="n">
         <v>47.9</v>
@@ -9878,8 +10058,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9918,7 +10106,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -9942,7 +10130,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>29.8</v>
+        <v>31.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9966,7 +10154,7 @@
         <v>21.5</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S16" t="n">
         <v>59.8</v>
@@ -10154,8 +10342,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10194,7 +10390,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10218,7 +10414,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.1</v>
+        <v>31.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,7 +10428,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -10242,10 +10438,10 @@
         <v>28.5</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
@@ -10255,39 +10451,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10430,8 +10622,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10470,7 +10670,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10494,7 +10694,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>24.7</v>
+        <v>26.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10518,7 +10718,7 @@
         <v>21.5</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S18" t="n">
         <v>71.7</v>
@@ -10706,8 +10906,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10746,7 +10954,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10770,7 +10978,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>24.6</v>
+        <v>26.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10794,7 +11002,7 @@
         <v>20.1</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S19" t="n">
         <v>40.2</v>
@@ -10982,8 +11190,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Progressive Field</t>

--- a/outputs/daily/hr_rankings_2026-10-18_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-18_full.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>53.6</v>
+        <v>54</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -811,7 +811,7 @@
         <v>41.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>78</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1628,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.8</v>
+        <v>47.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1642,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1655,7 +1651,7 @@
         <v>41.1</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
@@ -1665,39 +1661,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1863,12 +1855,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1893,7 +1885,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1912,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>45.3</v>
+        <v>46.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1926,11 +1918,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>41</v>
+        <v>43.3</v>
       </c>
       <c r="Q6" t="n">
         <v>21.5</v>
@@ -1939,49 +1931,45 @@
         <v>41.1</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>20.9</v>
+        <v>0</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2001,12 +1989,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2016,7 +2004,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2031,67 +2019,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2147,12 +2135,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2177,7 +2165,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2196,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>45.3</v>
+        <v>46</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2210,11 +2198,11 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
         <v>21.5</v>
@@ -2223,49 +2211,45 @@
         <v>41.1</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T7" t="n">
         <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2285,12 +2269,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2300,7 +2284,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2315,67 +2299,67 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -3551,24 +3535,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -3581,26 +3565,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>36.8</v>
+        <v>36.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3614,62 +3598,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R12" t="n">
         <v>41.1</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>70.59999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3689,27 +3669,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3719,97 +3699,97 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -3835,24 +3815,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -3865,26 +3845,26 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>36.4</v>
+        <v>36</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3898,26 +3878,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.9</v>
+        <v>10.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R13" t="n">
         <v>41.1</v>
       </c>
       <c r="S13" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>43.1</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3931,7 +3911,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3969,27 +3949,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3999,97 +3979,97 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -4395,24 +4375,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -4430,21 +4410,21 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.8</v>
+        <v>31.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4458,62 +4438,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>7.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R15" t="n">
         <v>41.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8</v>
+        <v>38.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4533,12 +4509,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4548,12 +4524,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4563,97 +4539,97 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
@@ -4679,12 +4655,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4709,7 +4685,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4728,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.9</v>
+        <v>29.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4742,11 +4718,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>12.8</v>
+        <v>11.6</v>
       </c>
       <c r="Q16" t="n">
         <v>21.5</v>
@@ -4755,49 +4731,45 @@
         <v>41.1</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
         <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4822,17 +4794,17 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -4847,67 +4819,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -4963,24 +4935,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -4993,26 +4965,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.8</v>
+        <v>28.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5026,26 +4998,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>7.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R17" t="n">
         <v>41.1</v>
       </c>
       <c r="S17" t="n">
-        <v>52.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>38.3</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -5059,7 +5031,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -5097,12 +5069,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5112,12 +5084,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5127,97 +5099,97 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
@@ -5243,12 +5215,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5273,7 +5245,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5292,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>26.7</v>
+        <v>28.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5306,11 +5278,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>7.8</v>
       </c>
       <c r="Q18" t="n">
         <v>21.5</v>
@@ -5319,49 +5291,45 @@
         <v>41.1</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5386,7 +5354,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5396,7 +5364,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -5411,67 +5379,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -5576,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.6</v>
+        <v>27.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5590,7 +5558,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5603,7 +5571,7 @@
         <v>41.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -5613,39 +5581,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6167,7 +6131,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6186,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>53.6</v>
+        <v>54</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6200,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6213,7 +6177,7 @@
         <v>41.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>78</v>
@@ -6223,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7030,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.8</v>
+        <v>47.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7044,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -7057,7 +7017,7 @@
         <v>41.1</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
@@ -7067,39 +7027,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7265,12 +7221,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7295,7 +7251,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -7314,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>45.3</v>
+        <v>46.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7328,11 +7284,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>41</v>
+        <v>43.3</v>
       </c>
       <c r="Q6" t="n">
         <v>21.5</v>
@@ -7341,49 +7297,45 @@
         <v>41.1</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>20.9</v>
+        <v>0</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7403,12 +7355,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -7418,7 +7370,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -7433,67 +7385,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -7549,12 +7501,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -7579,7 +7531,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -7598,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>45.3</v>
+        <v>46</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7612,11 +7564,11 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
         <v>21.5</v>
@@ -7625,49 +7577,45 @@
         <v>41.1</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T7" t="n">
         <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7687,12 +7635,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -7702,7 +7650,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -7717,67 +7665,67 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -8953,24 +8901,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -8983,26 +8931,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>36.8</v>
+        <v>36.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9016,62 +8964,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R12" t="n">
         <v>41.1</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>70.59999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9091,27 +9035,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -9121,97 +9065,97 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -9237,24 +9181,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -9267,26 +9211,26 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>36.4</v>
+        <v>36</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9300,26 +9244,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.9</v>
+        <v>10.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R13" t="n">
         <v>41.1</v>
       </c>
       <c r="S13" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>43.1</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -9333,7 +9277,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -9371,27 +9315,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9401,97 +9345,97 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -9797,24 +9741,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -9832,21 +9776,21 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.8</v>
+        <v>31.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9860,62 +9804,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>7.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R15" t="n">
         <v>41.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8</v>
+        <v>38.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9935,12 +9875,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9950,12 +9890,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9965,97 +9905,97 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
@@ -10081,12 +10021,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10111,7 +10051,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -10130,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.9</v>
+        <v>29.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10144,11 +10084,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>12.8</v>
+        <v>11.6</v>
       </c>
       <c r="Q16" t="n">
         <v>21.5</v>
@@ -10157,49 +10097,45 @@
         <v>41.1</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
         <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10224,17 +10160,17 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -10249,67 +10185,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -10365,24 +10301,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -10395,26 +10331,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.8</v>
+        <v>28.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10428,26 +10364,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>7.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R17" t="n">
         <v>41.1</v>
       </c>
       <c r="S17" t="n">
-        <v>52.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>38.3</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -10461,7 +10397,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -10499,12 +10435,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -10514,12 +10450,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10529,97 +10465,97 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
@@ -10645,12 +10581,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -10675,7 +10611,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -10694,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>26.7</v>
+        <v>28.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10708,11 +10644,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>7.8</v>
       </c>
       <c r="Q18" t="n">
         <v>21.5</v>
@@ -10721,49 +10657,45 @@
         <v>41.1</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10788,7 +10720,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10798,7 +10730,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -10813,67 +10745,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -10978,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.6</v>
+        <v>27.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10992,7 +10924,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -11005,7 +10937,7 @@
         <v>41.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -11015,39 +10947,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/daily/hr_rankings_2026-10-18_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-18_full.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>54.3</v>
+        <v>54.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>21.5</v>
       </c>
       <c r="R2" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50.4</v>
+        <v>50.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>28.5</v>
       </c>
       <c r="R3" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S3" t="n">
         <v>94.90000000000001</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.4</v>
+        <v>48.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>28.5</v>
       </c>
       <c r="R4" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S4" t="n">
         <v>96.59999999999999</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>47.7</v>
+        <v>47.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>21.5</v>
       </c>
       <c r="R5" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.3</v>
+        <v>46.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>21.5</v>
       </c>
       <c r="R7" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S7" t="n">
         <v>93.2</v>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>28.5</v>
       </c>
       <c r="R8" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S8" t="n">
         <v>86.40000000000001</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>43.3</v>
+        <v>43.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>26.9</v>
       </c>
       <c r="R9" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>41.8</v>
+        <v>42</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>26.9</v>
       </c>
       <c r="R10" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.7</v>
+        <v>38.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>28.5</v>
       </c>
       <c r="R11" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>36.7</v>
+        <v>36.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>28.5</v>
       </c>
       <c r="R12" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S12" t="n">
         <v>93.2</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>36.3</v>
+        <v>36.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>21.5</v>
       </c>
       <c r="R13" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S13" t="n">
         <v>76.2</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>34.1</v>
+        <v>34.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>26.9</v>
       </c>
       <c r="R14" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S14" t="n">
         <v>44.8</v>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.1</v>
+        <v>32.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>28.5</v>
       </c>
       <c r="R15" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S15" t="n">
         <v>52.4</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>29.8</v>
+        <v>30.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>21.5</v>
       </c>
       <c r="R16" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S16" t="n">
         <v>52.4</v>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.1</v>
+        <v>29.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>21.5</v>
       </c>
       <c r="R17" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S17" t="n">
         <v>86.40000000000001</v>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.7</v>
+        <v>28.9</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>21.5</v>
       </c>
       <c r="R18" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S18" t="n">
         <v>64.3</v>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>27.5</v>
+        <v>27.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>20.1</v>
       </c>
       <c r="R19" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>54.3</v>
+        <v>54.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>21.5</v>
       </c>
       <c r="R2" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50.4</v>
+        <v>50.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>28.5</v>
       </c>
       <c r="R3" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S3" t="n">
         <v>94.90000000000001</v>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.4</v>
+        <v>48.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>28.5</v>
       </c>
       <c r="R4" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S4" t="n">
         <v>96.59999999999999</v>
@@ -6925,7 +6925,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>47.7</v>
+        <v>47.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>21.5</v>
       </c>
       <c r="R5" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.3</v>
+        <v>46.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>21.5</v>
       </c>
       <c r="R7" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S7" t="n">
         <v>93.2</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>28.5</v>
       </c>
       <c r="R8" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S8" t="n">
         <v>86.40000000000001</v>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>43.3</v>
+        <v>43.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>26.9</v>
       </c>
       <c r="R9" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -8325,7 +8325,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>41.8</v>
+        <v>42</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>26.9</v>
       </c>
       <c r="R10" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.7</v>
+        <v>38.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>28.5</v>
       </c>
       <c r="R11" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>36.7</v>
+        <v>36.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>28.5</v>
       </c>
       <c r="R12" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S12" t="n">
         <v>93.2</v>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>36.3</v>
+        <v>36.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>21.5</v>
       </c>
       <c r="R13" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S13" t="n">
         <v>76.2</v>
@@ -9445,7 +9445,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>34.1</v>
+        <v>34.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>26.9</v>
       </c>
       <c r="R14" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S14" t="n">
         <v>44.8</v>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.1</v>
+        <v>32.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>28.5</v>
       </c>
       <c r="R15" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S15" t="n">
         <v>52.4</v>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>29.8</v>
+        <v>30.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>21.5</v>
       </c>
       <c r="R16" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S16" t="n">
         <v>52.4</v>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.1</v>
+        <v>29.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>21.5</v>
       </c>
       <c r="R17" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S17" t="n">
         <v>86.40000000000001</v>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.7</v>
+        <v>28.9</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>21.5</v>
       </c>
       <c r="R18" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S18" t="n">
         <v>64.3</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>27.5</v>
+        <v>27.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>20.1</v>
       </c>
       <c r="R19" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
